--- a/manual_cropped_sounds/8_00_date/0000/0000.xlsx
+++ b/manual_cropped_sounds/8_00_date/0000/0000.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefa\BovineTalk\Sunete PED separare vaca vitel\8_00_date\0000\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bovine_Talk\8_00_date\0000\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97CEC38B-F87B-43F3-9692-FA276009869E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C6C75C3-964A-42B6-9B13-F11AF1130F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B0C9348E-2B10-46A9-9B69-BE587A5A529A}"/>
+    <workbookView xWindow="4920" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{B0C9348E-2B10-46A9-9B69-BE587A5A529A}"/>
   </bookViews>
   <sheets>
     <sheet name="out" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <definedName name="ExternalData_1" localSheetId="0" hidden="1">out!$A$1:$AF$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -347,9 +348,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -780,36 +780,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B61119-2F92-466D-9DF2-1FD29D615FBB}">
   <dimension ref="A1:AF28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.53125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.46484375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.53125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.796875" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.46484375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.46484375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.46484375" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="14.1328125" bestFit="1" customWidth="1"/>
     <col min="28" max="29" width="22" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.46484375" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -907,8 +907,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>32</v>
       </c>
       <c r="B2">
@@ -941,7 +941,7 @@
       <c r="K2">
         <v>0.71399999999999997</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" t="s">
         <v>33</v>
       </c>
       <c r="M2">
@@ -998,15 +998,15 @@
       <c r="AD2">
         <v>-2.9289999999999998</v>
       </c>
-      <c r="AE2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AE2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
         <v>35</v>
       </c>
       <c r="B3">
@@ -1039,7 +1039,7 @@
       <c r="K3">
         <v>2.6930000000000001</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" t="s">
         <v>36</v>
       </c>
       <c r="M3">
@@ -1096,15 +1096,15 @@
       <c r="AD3">
         <v>0.14699999999999999</v>
       </c>
-      <c r="AE3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF3" s="1" t="s">
+      <c r="AE3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
         <v>37</v>
       </c>
       <c r="B4">
@@ -1137,7 +1137,7 @@
       <c r="K4">
         <v>1.6639999999999999</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" t="s">
         <v>38</v>
       </c>
       <c r="M4">
@@ -1194,15 +1194,15 @@
       <c r="AD4">
         <v>-0.20699999999999999</v>
       </c>
-      <c r="AE4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF4" s="1" t="s">
+      <c r="AE4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>39</v>
       </c>
       <c r="B5">
@@ -1235,7 +1235,7 @@
       <c r="K5">
         <v>4.7690000000000001</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" t="s">
         <v>40</v>
       </c>
       <c r="M5">
@@ -1292,15 +1292,15 @@
       <c r="AD5">
         <v>-0.25900000000000001</v>
       </c>
-      <c r="AE5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF5" s="1" t="s">
+      <c r="AE5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
         <v>41</v>
       </c>
       <c r="B6">
@@ -1333,7 +1333,7 @@
       <c r="K6">
         <v>4.6020000000000003</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" t="s">
         <v>42</v>
       </c>
       <c r="M6">
@@ -1390,15 +1390,15 @@
       <c r="AD6">
         <v>-2.395</v>
       </c>
-      <c r="AE6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF6" s="1" t="s">
+      <c r="AE6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
         <v>43</v>
       </c>
       <c r="B7">
@@ -1431,7 +1431,7 @@
       <c r="K7">
         <v>3.6760000000000002</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" t="s">
         <v>44</v>
       </c>
       <c r="M7">
@@ -1488,15 +1488,15 @@
       <c r="AD7">
         <v>-0.96199999999999997</v>
       </c>
-      <c r="AE7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF7" s="1" t="s">
+      <c r="AE7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
         <v>45</v>
       </c>
       <c r="B8">
@@ -1529,7 +1529,7 @@
       <c r="K8">
         <v>2.8159999999999998</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" t="s">
         <v>46</v>
       </c>
       <c r="M8">
@@ -1586,15 +1586,15 @@
       <c r="AD8">
         <v>-1.1519999999999999</v>
       </c>
-      <c r="AE8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF8" s="1" t="s">
+      <c r="AE8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
         <v>47</v>
       </c>
       <c r="B9">
@@ -1627,7 +1627,7 @@
       <c r="K9">
         <v>0</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" t="s">
         <v>48</v>
       </c>
       <c r="M9">
@@ -1684,15 +1684,15 @@
       <c r="AD9">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="AE9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF9" s="1" t="s">
+      <c r="AE9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
         <v>49</v>
       </c>
       <c r="B10">
@@ -1725,7 +1725,7 @@
       <c r="K10">
         <v>3.8809999999999998</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10" t="s">
         <v>50</v>
       </c>
       <c r="M10">
@@ -1782,15 +1782,15 @@
       <c r="AD10">
         <v>-1.4450000000000001</v>
       </c>
-      <c r="AE10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF10" s="1" t="s">
+      <c r="AE10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
         <v>51</v>
       </c>
       <c r="B11">
@@ -1823,7 +1823,7 @@
       <c r="K11">
         <v>1.0509999999999999</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="L11" t="s">
         <v>52</v>
       </c>
       <c r="M11">
@@ -1880,15 +1880,15 @@
       <c r="AD11">
         <v>-0.21199999999999999</v>
       </c>
-      <c r="AE11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF11" s="1" t="s">
+      <c r="AE11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
         <v>53</v>
       </c>
       <c r="B12">
@@ -1921,7 +1921,7 @@
       <c r="K12">
         <v>2.6819999999999999</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="L12" t="s">
         <v>54</v>
       </c>
       <c r="M12">
@@ -1978,15 +1978,15 @@
       <c r="AD12">
         <v>-1.9550000000000001</v>
       </c>
-      <c r="AE12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF12" s="1" t="s">
+      <c r="AE12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
         <v>55</v>
       </c>
       <c r="B13">
@@ -2019,7 +2019,7 @@
       <c r="K13">
         <v>2.3980000000000001</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="L13" t="s">
         <v>56</v>
       </c>
       <c r="M13">
@@ -2076,15 +2076,15 @@
       <c r="AD13">
         <v>-0.60199999999999998</v>
       </c>
-      <c r="AE13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF13" s="1" t="s">
+      <c r="AE13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
         <v>57</v>
       </c>
       <c r="B14">
@@ -2117,7 +2117,7 @@
       <c r="K14">
         <v>3.37</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="L14" t="s">
         <v>58</v>
       </c>
       <c r="M14">
@@ -2174,15 +2174,15 @@
       <c r="AD14">
         <v>-1.4510000000000001</v>
       </c>
-      <c r="AE14" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF14" s="1" t="s">
+      <c r="AE14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
         <v>59</v>
       </c>
       <c r="B15">
@@ -2215,7 +2215,7 @@
       <c r="K15">
         <v>5.3940000000000001</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="L15" t="s">
         <v>60</v>
       </c>
       <c r="M15">
@@ -2272,15 +2272,15 @@
       <c r="AD15">
         <v>-1.6259999999999999</v>
       </c>
-      <c r="AE15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF15" s="1" t="s">
+      <c r="AE15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
         <v>61</v>
       </c>
       <c r="B16">
@@ -2313,7 +2313,7 @@
       <c r="K16">
         <v>4.91</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="L16" t="s">
         <v>62</v>
       </c>
       <c r="M16">
@@ -2370,15 +2370,15 @@
       <c r="AD16">
         <v>-1.242</v>
       </c>
-      <c r="AE16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF16" s="1" t="s">
+      <c r="AE16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
         <v>63</v>
       </c>
       <c r="B17">
@@ -2411,7 +2411,7 @@
       <c r="K17">
         <v>4.1360000000000001</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="L17" t="s">
         <v>64</v>
       </c>
       <c r="M17">
@@ -2468,15 +2468,15 @@
       <c r="AD17">
         <v>-1.764</v>
       </c>
-      <c r="AE17" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF17" s="1" t="s">
+      <c r="AE17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF17" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
         <v>65</v>
       </c>
       <c r="B18">
@@ -2509,7 +2509,7 @@
       <c r="K18">
         <v>4.3520000000000003</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="L18" t="s">
         <v>66</v>
       </c>
       <c r="M18">
@@ -2566,15 +2566,15 @@
       <c r="AD18">
         <v>-1.327</v>
       </c>
-      <c r="AE18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF18" s="1" t="s">
+      <c r="AE18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
         <v>67</v>
       </c>
       <c r="B19">
@@ -2607,7 +2607,7 @@
       <c r="K19">
         <v>3.8860000000000001</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="L19" t="s">
         <v>68</v>
       </c>
       <c r="M19">
@@ -2664,15 +2664,15 @@
       <c r="AD19">
         <v>-1.0229999999999999</v>
       </c>
-      <c r="AE19" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF19" s="1" t="s">
+      <c r="AE19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
         <v>69</v>
       </c>
       <c r="B20">
@@ -2705,7 +2705,7 @@
       <c r="K20">
         <v>3.1669999999999998</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="L20" t="s">
         <v>70</v>
       </c>
       <c r="M20">
@@ -2762,15 +2762,15 @@
       <c r="AD20">
         <v>-0.55200000000000005</v>
       </c>
-      <c r="AE20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF20" s="1" t="s">
+      <c r="AE20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF20" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
         <v>71</v>
       </c>
       <c r="B21">
@@ -2803,7 +2803,7 @@
       <c r="K21">
         <v>2.266</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="L21" t="s">
         <v>72</v>
       </c>
       <c r="M21">
@@ -2860,15 +2860,15 @@
       <c r="AD21">
         <v>-2.2989999999999999</v>
       </c>
-      <c r="AE21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF21" s="1" t="s">
+      <c r="AE21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF21" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
         <v>73</v>
       </c>
       <c r="B22">
@@ -2901,7 +2901,7 @@
       <c r="K22">
         <v>2.5939999999999999</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="L22" t="s">
         <v>74</v>
       </c>
       <c r="M22">
@@ -2958,15 +2958,15 @@
       <c r="AD22">
         <v>-0.69</v>
       </c>
-      <c r="AE22" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF22" s="1" t="s">
+      <c r="AE22" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF22" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
         <v>75</v>
       </c>
       <c r="B23">
@@ -2999,7 +2999,7 @@
       <c r="K23">
         <v>2.754</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="L23" t="s">
         <v>76</v>
       </c>
       <c r="M23">
@@ -3056,15 +3056,15 @@
       <c r="AD23">
         <v>-2.6909999999999998</v>
       </c>
-      <c r="AE23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF23" s="1" t="s">
+      <c r="AE23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF23" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
         <v>77</v>
       </c>
       <c r="B24">
@@ -3097,7 +3097,7 @@
       <c r="K24">
         <v>2.1309999999999998</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="L24" t="s">
         <v>78</v>
       </c>
       <c r="M24">
@@ -3154,15 +3154,15 @@
       <c r="AD24">
         <v>-0.38800000000000001</v>
       </c>
-      <c r="AE24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF24" s="1" t="s">
+      <c r="AE24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF24" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
         <v>79</v>
       </c>
       <c r="B25">
@@ -3195,7 +3195,7 @@
       <c r="K25">
         <v>3.3130000000000002</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="L25" t="s">
         <v>80</v>
       </c>
       <c r="M25">
@@ -3252,15 +3252,15 @@
       <c r="AD25">
         <v>-1.57</v>
       </c>
-      <c r="AE25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF25" s="1" t="s">
+      <c r="AE25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF25" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
         <v>81</v>
       </c>
       <c r="B26">
@@ -3293,7 +3293,7 @@
       <c r="K26">
         <v>2.5270000000000001</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="L26" t="s">
         <v>82</v>
       </c>
       <c r="M26">
@@ -3350,15 +3350,15 @@
       <c r="AD26">
         <v>-2.847</v>
       </c>
-      <c r="AE26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF26" s="1" t="s">
+      <c r="AE26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF26" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
         <v>83</v>
       </c>
       <c r="B27">
@@ -3391,7 +3391,7 @@
       <c r="K27">
         <v>1.3140000000000001</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="L27" t="s">
         <v>84</v>
       </c>
       <c r="M27">
@@ -3448,15 +3448,15 @@
       <c r="AD27">
         <v>-1.1950000000000001</v>
       </c>
-      <c r="AE27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF27" s="1" t="s">
+      <c r="AE27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF27" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
         <v>85</v>
       </c>
       <c r="B28">
@@ -3489,7 +3489,7 @@
       <c r="K28">
         <v>1.341</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="L28" t="s">
         <v>86</v>
       </c>
       <c r="M28">
@@ -3546,10 +3546,10 @@
       <c r="AD28">
         <v>-0.89900000000000002</v>
       </c>
-      <c r="AE28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF28" s="1" t="s">
+      <c r="AE28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF28" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F95DCAB-249F-48E1-8DDB-0C485C8D9AD4}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
